--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,62 +796,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79907177</v>
+        <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ladskär NV om Öregrund, Upl</t>
+          <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682793.5932856956</v>
+        <v>682607</v>
       </c>
       <c r="R3" t="n">
-        <v>6696396.024745935</v>
+        <v>6696356</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca. 5 ex. under gran.</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,39 +884,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79907176</v>
+        <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,46 +913,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4363</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ladskär NV om Öregrund, Upl</t>
+          <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682807.7309830581</v>
+        <v>682644</v>
       </c>
       <c r="R4" t="n">
-        <v>6696391.285032155</v>
+        <v>6696335</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1007,27 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ca. 50 ex. under gran.</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,31 +992,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79907174</v>
+        <v>79907177</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
+        <v>85278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,34 +1024,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6003295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ladskär NV om Öregrund, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>682827.4122421412</v>
+        <v>682793.5932856956</v>
       </c>
       <c r="R5" t="n">
-        <v>6696394.753744213</v>
+        <v>6696396.024745935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1107,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ganska rikligt, under granar.</t>
+          <t>Ca. 5 ex. under gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,6 +1116,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1181,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79907178</v>
+        <v>79907176</v>
       </c>
       <c r="B6" t="n">
-        <v>90126</v>
+        <v>90649</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,30 +1152,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232138</v>
+        <v>4363</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1230,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682827.4122421412</v>
+        <v>682807.7309830581</v>
       </c>
       <c r="R6" t="n">
-        <v>6696394.753744213</v>
+        <v>6696391.285032155</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1239,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca. 5 ex. under gran.</t>
+          <t>Ca. 50 ex. under gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,6 +1268,564 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>79907174</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90697</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ladskär NV om Öregrund, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>682827.4122421412</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6696394.753744213</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ganska rikligt, under granar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>79907178</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90126</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ladskär NV om Öregrund, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>682827.4122421412</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6696394.753744213</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125747260</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110404</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ladskär, Ladskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>682789</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6696346</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125747623</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ladskär, Ladskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>682783</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6696339</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125747395</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ladskär, Ladskär, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>682783</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6696334</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110404</v>
+        <v>110411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98353</v>
+        <v>98356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110411</v>
+        <v>110414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98353</v>
+        <v>98356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98353</v>
+        <v>98356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110414</v>
+        <v>110418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110418</v>
+        <v>110419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110419</v>
+        <v>110421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110421</v>
+        <v>110423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98363</v>
+        <v>98365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110423</v>
+        <v>110427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110427</v>
+        <v>110440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>125783793</v>
       </c>
       <c r="B3" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>125783460</v>
       </c>
       <c r="B4" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>125747260</v>
       </c>
       <c r="B9" t="n">
-        <v>110440</v>
+        <v>110443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>125747623</v>
       </c>
       <c r="B10" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>125747395</v>
       </c>
       <c r="B11" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110213448</v>
+        <v>79907176</v>
       </c>
       <c r="B2" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ladskär, Upl</t>
+          <t>Ladskär NV om Öregrund, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682644.6178273135</v>
+        <v>682808</v>
       </c>
       <c r="R2" t="n">
-        <v>6696328.067899413</v>
+        <v>6696391</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ca. 50 ex. under gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,29 +768,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125783793</v>
+        <v>99425842</v>
       </c>
       <c r="B3" t="n">
-        <v>98374</v>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -829,24 +824,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ladskär, Ladskär, Upl</t>
+          <t>Ladskär, Kallrigafjärden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682607</v>
+        <v>682730</v>
       </c>
       <c r="R3" t="n">
-        <v>6696356</v>
+        <v>6696366</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,12 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,66 +892,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Vilhelm Peterson Lithell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Vilhelm Peterson Lithell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125783460</v>
+        <v>125747260</v>
       </c>
       <c r="B4" t="n">
-        <v>98374</v>
+        <v>111390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>682644</v>
+        <v>682789</v>
       </c>
       <c r="R4" t="n">
-        <v>6696335</v>
+        <v>6696346</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,12 +969,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,62 +1001,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79907177</v>
+        <v>110213448</v>
       </c>
       <c r="B5" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ladskär NV om Öregrund, Upl</t>
+          <t>Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>682793.5932856956</v>
+        <v>682645</v>
       </c>
       <c r="R5" t="n">
-        <v>6696396.024745935</v>
+        <v>6696328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,27 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca. 5 ex. under gran.</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,35 +1092,25 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79907176</v>
+        <v>125747395</v>
       </c>
       <c r="B6" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,46 +1118,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ladskär NV om Öregrund, Upl</t>
+          <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>682807.7309830581</v>
+        <v>682783</v>
       </c>
       <c r="R6" t="n">
-        <v>6696391.285032155</v>
+        <v>6696334</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,27 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ca. 50 ex. under gran.</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,74 +1188,78 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79907174</v>
+        <v>125747623</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ladskär NV om Öregrund, Upl</t>
+          <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>682827.4122421412</v>
+        <v>682783</v>
       </c>
       <c r="R7" t="n">
-        <v>6696394.753744213</v>
+        <v>6696339</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,27 +1283,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ganska rikligt, under granar.</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,83 +1299,73 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79907178</v>
+        <v>125783460</v>
       </c>
       <c r="B8" t="n">
-        <v>90126</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232138</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ladskär NV om Öregrund, Upl</t>
+          <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>682827.4122421412</v>
+        <v>682644</v>
       </c>
       <c r="R8" t="n">
-        <v>6696394.753744213</v>
+        <v>6696335</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,27 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca. 5 ex. under gran.</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,31 +1405,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Äldre, örtrik granskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125747260</v>
+        <v>125783580</v>
       </c>
       <c r="B9" t="n">
-        <v>110443</v>
+        <v>99141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,34 +1432,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ladskär, Ladskär, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>682789</v>
+        <v>682607</v>
       </c>
       <c r="R9" t="n">
-        <v>6696346</v>
+        <v>6696356</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1589,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,62 +1527,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125747623</v>
+        <v>79907178</v>
       </c>
       <c r="B10" t="n">
-        <v>98374</v>
+        <v>92688</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>232138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Gul lammticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Albatrellus citrinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Ryman</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ladskär, Ladskär, Upl</t>
+          <t>Ladskär NV om Öregrund, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>682783</v>
+        <v>682827</v>
       </c>
       <c r="R10" t="n">
-        <v>6696339</v>
+        <v>6696395</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,12 +1601,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. under gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,64 +1622,78 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125747395</v>
+        <v>79907177</v>
       </c>
       <c r="B11" t="n">
-        <v>98374</v>
+        <v>87346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219862</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ladskär, Ladskär, Upl</t>
+          <t>Ladskär NV om Öregrund, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>682783</v>
+        <v>682794</v>
       </c>
       <c r="R11" t="n">
-        <v>6696334</v>
+        <v>6696396</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,12 +1717,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2019-08-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. under gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,18 +1736,24 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre, örtrik granskog.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Gillis Aronsson, Ralf Lundmark, Elisabet Odhult, Maria Hoflin, Fredrik Söderman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 48277-2023 artfynd.xlsx
+++ b/artfynd/A 48277-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79907176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99425842</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110213448</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747395</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125747623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783460</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125783580</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79907178</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,8 +1807,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79907177</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>